--- a/data/xlsx/basis--ui-ux-design-it-sector.xlsx
+++ b/data/xlsx/basis--ui-ux-design-it-sector.xlsx
@@ -667,7 +667,7 @@
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel Core i5 processor, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (24-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (24-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">

--- a/data/xlsx/basis--ui-ux-design-it-sector.xlsx
+++ b/data/xlsx/basis--ui-ux-design-it-sector.xlsx
@@ -667,7 +667,7 @@
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (24-inch minimum, with color accuracy).</t>
+(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (24-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">

--- a/data/xlsx/basis--ui-ux-design-it-sector.xlsx
+++ b/data/xlsx/basis--ui-ux-design-it-sector.xlsx
@@ -667,7 +667,7 @@
       <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Computers/Laptop: 
-(Minimum Intel core i5 or Intel core i3 6 gen/above, or AMD Ryzen similar spec, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (24-inch minimum, with color accuracy).</t>
+(Minimum Intel Core i5 processor, 8GB RAM (16GB preferred), 500GB SSD storage (1TB preferred), High-resolution monitors (24-inch minimum, with color accuracy).</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
